--- a/data/00403A_20260826.xlsx
+++ b/data/00403A_20260826.xlsx
@@ -12,9 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="215">
-  <si>
-    <t xml:space="preserve">資料日期：115/08/25</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="213">
+  <si>
+    <t xml:space="preserve">資料日期：115/08/26</t>
   </si>
   <si>
     <t xml:space="preserve">基金資產</t>
@@ -23,19 +23,19 @@
     <t xml:space="preserve">淨資產</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 168,071,796,729</t>
+    <t xml:space="preserve">NTD 171,775,949,905</t>
   </si>
   <si>
     <t xml:space="preserve">流通在外單位數</t>
   </si>
   <si>
-    <t xml:space="preserve">16,847,019,000</t>
+    <t xml:space="preserve">16,813,519,000</t>
   </si>
   <si>
     <t xml:space="preserve">每單位淨值</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 9.98</t>
+    <t xml:space="preserve">NTD 10.22</t>
   </si>
   <si>
     <t xml:space="preserve">項目</t>
@@ -59,16 +59,16 @@
     <t xml:space="preserve">股票</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 150,231,431,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.39%</t>
+    <t xml:space="preserve">NTD 155,065,632,500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.27%</t>
   </si>
   <si>
     <t xml:space="preserve">現金</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 10,178,153,121</t>
+    <t xml:space="preserve">NTD 10,569,798,466</t>
   </si>
   <si>
     <t xml:space="preserve">期貨保證金</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">附買回債券</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 5,737,461,838</t>
+    <t xml:space="preserve">NTD 5,457,566,030</t>
   </si>
   <si>
     <t xml:space="preserve">應收付證券款</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 87,354,442</t>
+    <t xml:space="preserve">NTD -479,094,741</t>
   </si>
   <si>
     <t xml:space="preserve">股票代號</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">12,000,000</t>
   </si>
   <si>
-    <t xml:space="preserve">17.14%</t>
+    <t xml:space="preserve">16.87%</t>
   </si>
   <si>
     <t xml:space="preserve">2383</t>
@@ -119,7 +119,19 @@
     <t xml:space="preserve">1,690,000</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63%</t>
+    <t xml:space="preserve">5.80%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奇鋐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,150,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79%</t>
   </si>
   <si>
     <t xml:space="preserve">3037</t>
@@ -131,19 +143,7 @@
     <t xml:space="preserve">8,460,000</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">奇鋐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,100,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44%</t>
+    <t xml:space="preserve">5.71%</t>
   </si>
   <si>
     <t xml:space="preserve">2454</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">2,110,000</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69%</t>
+    <t xml:space="preserve">4.85%</t>
   </si>
   <si>
     <t xml:space="preserve">2303</t>
@@ -167,7 +167,19 @@
     <t xml:space="preserve">60,000,000</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46%</t>
+    <t xml:space="preserve">4.31%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">健策</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,087,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62%</t>
   </si>
   <si>
     <t xml:space="preserve">6223</t>
@@ -179,19 +191,7 @@
     <t xml:space="preserve">1,100,000</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">健策</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,080,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34%</t>
+    <t xml:space="preserve">3.23%</t>
   </si>
   <si>
     <t xml:space="preserve">2327</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">9,785,000</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17%</t>
+    <t xml:space="preserve">3.06%</t>
   </si>
   <si>
     <t xml:space="preserve">2308</t>
@@ -212,10 +212,22 @@
     <t xml:space="preserve">台達電</t>
   </si>
   <si>
-    <t xml:space="preserve">3,040,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09%</t>
+    <t xml:space="preserve">2,880,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">智邦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,307,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76%</t>
   </si>
   <si>
     <t xml:space="preserve">3711</t>
@@ -227,31 +239,28 @@
     <t xml:space="preserve">8,000,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">智邦</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,307,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79%</t>
-  </si>
-  <si>
     <t xml:space="preserve">6669</t>
   </si>
   <si>
     <t xml:space="preserve">緯穎</t>
   </si>
   <si>
-    <t xml:space="preserve">630,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41%</t>
+    <t xml:space="preserve">660,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">景碩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,550,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33%</t>
   </si>
   <si>
     <t xml:space="preserve">3008</t>
@@ -263,19 +272,7 @@
     <t xml:space="preserve">626,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">景碩</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,250,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11%</t>
+    <t xml:space="preserve">2.29%</t>
   </si>
   <si>
     <t xml:space="preserve">3443</t>
@@ -284,10 +281,10 @@
     <t xml:space="preserve">創意</t>
   </si>
   <si>
-    <t xml:space="preserve">610,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02%</t>
+    <t xml:space="preserve">621,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21%</t>
   </si>
   <si>
     <t xml:space="preserve">8046</t>
@@ -299,7 +296,19 @@
     <t xml:space="preserve">2,640,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82%</t>
+    <t xml:space="preserve">1.81%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台燿</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,900,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69%</t>
   </si>
   <si>
     <t xml:space="preserve">5274</t>
@@ -314,6 +323,18 @@
     <t xml:space="preserve">1.64%</t>
   </si>
   <si>
+    <t xml:space="preserve">2344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">華邦電</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,000,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58%</t>
+  </si>
+  <si>
     <t xml:space="preserve">6488</t>
   </si>
   <si>
@@ -323,31 +344,7 @@
     <t xml:space="preserve">2,800,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">華邦電</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,000,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">台燿</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,800,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59%</t>
+    <t xml:space="preserve">1.55%</t>
   </si>
   <si>
     <t xml:space="preserve">3665</t>
@@ -359,7 +356,19 @@
     <t xml:space="preserve">1,200,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48%</t>
+    <t xml:space="preserve">1.40%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南亞</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,358,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25%</t>
   </si>
   <si>
     <t xml:space="preserve">8996</t>
@@ -368,10 +377,10 @@
     <t xml:space="preserve">高力</t>
   </si>
   <si>
-    <t xml:space="preserve">1,720,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24%</t>
+    <t xml:space="preserve">1,737,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21%</t>
   </si>
   <si>
     <t xml:space="preserve">2360</t>
@@ -383,19 +392,19 @@
     <t xml:space="preserve">1,000,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">南亞</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,000,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12%</t>
+    <t xml:space="preserve">1.15%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">富世達</t>
+  </si>
+  <si>
+    <t xml:space="preserve">866,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02%</t>
   </si>
   <si>
     <t xml:space="preserve">6239</t>
@@ -407,19 +416,7 @@
     <t xml:space="preserve">5,360,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">富世達</t>
-  </si>
-  <si>
-    <t xml:space="preserve">780,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86%</t>
+    <t xml:space="preserve">0.89%</t>
   </si>
   <si>
     <t xml:space="preserve">7769</t>
@@ -455,7 +452,19 @@
     <t xml:space="preserve">2,000,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39%</t>
+    <t xml:space="preserve">0.42%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">辛耘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35%</t>
   </si>
   <si>
     <t xml:space="preserve">2337</t>
@@ -470,15 +479,6 @@
     <t xml:space="preserve">0.33%</t>
   </si>
   <si>
-    <t xml:space="preserve">3583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">辛耘</t>
-  </si>
-  <si>
-    <t xml:space="preserve">800,000</t>
-  </si>
-  <si>
     <t xml:space="preserve">2059</t>
   </si>
   <si>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">嘉澤</t>
   </si>
   <si>
-    <t xml:space="preserve">300,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29%</t>
+    <t xml:space="preserve">250,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24%</t>
   </si>
   <si>
     <t xml:space="preserve">6442</t>
@@ -521,9 +521,6 @@
     <t xml:space="preserve">金居</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20%</t>
-  </si>
-  <si>
     <t xml:space="preserve">1560</t>
   </si>
   <si>
@@ -542,9 +539,6 @@
     <t xml:space="preserve">漢唐</t>
   </si>
   <si>
-    <t xml:space="preserve">250,000</t>
-  </si>
-  <si>
     <t xml:space="preserve">4958</t>
   </si>
   <si>
@@ -575,7 +569,7 @@
     <t xml:space="preserve">2,500,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11%</t>
+    <t xml:space="preserve">0.10%</t>
   </si>
   <si>
     <t xml:space="preserve">3264</t>
@@ -1436,7 +1430,8 @@
   <dimension ref="A1:E70"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="24.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.35" bestFit="1" customWidth="1"/>
   </cols>
@@ -1745,287 +1740,287 @@
         <v>74</v>
       </c>
       <c r="D32" s="78" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="79" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="80" t="s">
         <v>76</v>
       </c>
-      <c r="B33" s="80" t="s">
+      <c r="C33" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="D33" s="82" t="s">
         <v>78</v>
-      </c>
-      <c r="D33" s="82" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="83" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="84" t="s">
+      <c r="C34" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="D34" s="86" t="s">
         <v>82</v>
-      </c>
-      <c r="D34" s="86" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="87" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="88" t="s">
         <v>84</v>
       </c>
-      <c r="B35" s="88" t="s">
+      <c r="C35" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="89" t="s">
+      <c r="D35" s="90" t="s">
         <v>86</v>
-      </c>
-      <c r="D35" s="90" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="91" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="92" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="92" t="s">
+      <c r="C36" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="93" t="s">
+      <c r="D36" s="94" t="s">
         <v>90</v>
-      </c>
-      <c r="D36" s="94" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="95" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="96" t="s">
         <v>92</v>
       </c>
-      <c r="B37" s="96" t="s">
+      <c r="C37" s="97" t="s">
         <v>93</v>
       </c>
-      <c r="C37" s="97" t="s">
+      <c r="D37" s="98" t="s">
         <v>94</v>
-      </c>
-      <c r="D37" s="98" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="99" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="100" t="s">
         <v>96</v>
       </c>
-      <c r="B38" s="100" t="s">
+      <c r="C38" s="101" t="s">
         <v>97</v>
       </c>
-      <c r="C38" s="101" t="s">
+      <c r="D38" s="102" t="s">
         <v>98</v>
-      </c>
-      <c r="D38" s="102" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="103" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="104" t="s">
         <v>100</v>
       </c>
-      <c r="B39" s="104" t="s">
+      <c r="C39" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="C39" s="105" t="s">
+      <c r="D39" s="106" t="s">
         <v>102</v>
-      </c>
-      <c r="D39" s="106" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="107" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="B40" s="108" t="s">
+      <c r="C40" s="109" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="109" t="s">
+      <c r="D40" s="110" t="s">
         <v>106</v>
-      </c>
-      <c r="D40" s="110" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="111" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="112" t="s">
         <v>108</v>
       </c>
-      <c r="B41" s="112" t="s">
+      <c r="C41" s="113" t="s">
         <v>109</v>
       </c>
-      <c r="C41" s="113" t="s">
+      <c r="D41" s="114" t="s">
         <v>110</v>
-      </c>
-      <c r="D41" s="114" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="115" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="B42" s="116" t="s">
+      <c r="C42" s="117" t="s">
         <v>113</v>
       </c>
-      <c r="C42" s="117" t="s">
+      <c r="D42" s="118" t="s">
         <v>114</v>
-      </c>
-      <c r="D42" s="118" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="119" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="120" t="s">
         <v>116</v>
       </c>
-      <c r="B43" s="120" t="s">
+      <c r="C43" s="121" t="s">
         <v>117</v>
       </c>
-      <c r="C43" s="121" t="s">
+      <c r="D43" s="122" t="s">
         <v>118</v>
-      </c>
-      <c r="D43" s="122" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="123" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" s="124" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="124" t="s">
+      <c r="C44" s="125" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="125" t="s">
+      <c r="D44" s="126" t="s">
         <v>122</v>
-      </c>
-      <c r="D44" s="126" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="127" t="s">
+        <v>123</v>
+      </c>
+      <c r="B45" s="128" t="s">
         <v>124</v>
       </c>
-      <c r="B45" s="128" t="s">
+      <c r="C45" s="129" t="s">
         <v>125</v>
       </c>
-      <c r="C45" s="129" t="s">
+      <c r="D45" s="130" t="s">
         <v>126</v>
-      </c>
-      <c r="D45" s="130" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="131" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" s="132" t="s">
         <v>128</v>
       </c>
-      <c r="B46" s="132" t="s">
+      <c r="C46" s="133" t="s">
         <v>129</v>
       </c>
-      <c r="C46" s="133" t="s">
+      <c r="D46" s="134" t="s">
         <v>130</v>
-      </c>
-      <c r="D46" s="134" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="135" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="136" t="s">
         <v>132</v>
       </c>
-      <c r="B47" s="136" t="s">
+      <c r="C47" s="137" t="s">
         <v>133</v>
       </c>
-      <c r="C47" s="137" t="s">
+      <c r="D47" s="138" t="s">
         <v>134</v>
-      </c>
-      <c r="D47" s="138" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="139" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" s="140" t="s">
         <v>136</v>
       </c>
-      <c r="B48" s="140" t="s">
+      <c r="C48" s="141" t="s">
         <v>137</v>
       </c>
-      <c r="C48" s="141" t="s">
+      <c r="D48" s="142" t="s">
         <v>138</v>
-      </c>
-      <c r="D48" s="142" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="143" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" s="144" t="s">
         <v>140</v>
       </c>
-      <c r="B49" s="144" t="s">
+      <c r="C49" s="145" t="s">
         <v>141</v>
       </c>
-      <c r="C49" s="145" t="s">
+      <c r="D49" s="146" t="s">
         <v>142</v>
-      </c>
-      <c r="D49" s="146" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="147" t="s">
+        <v>143</v>
+      </c>
+      <c r="B50" s="148" t="s">
         <v>144</v>
       </c>
-      <c r="B50" s="148" t="s">
+      <c r="C50" s="149" t="s">
         <v>145</v>
       </c>
-      <c r="C50" s="149" t="s">
+      <c r="D50" s="150" t="s">
         <v>146</v>
-      </c>
-      <c r="D50" s="150" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="151" t="s">
+        <v>147</v>
+      </c>
+      <c r="B51" s="152" t="s">
         <v>148</v>
       </c>
-      <c r="B51" s="152" t="s">
+      <c r="C51" s="153" t="s">
         <v>149</v>
       </c>
-      <c r="C51" s="153" t="s">
+      <c r="D51" s="154" t="s">
         <v>150</v>
-      </c>
-      <c r="D51" s="154" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="155" t="s">
+        <v>151</v>
+      </c>
+      <c r="B52" s="156" t="s">
         <v>152</v>
       </c>
-      <c r="B52" s="156" t="s">
+      <c r="C52" s="157" t="s">
         <v>153</v>
       </c>
-      <c r="C52" s="157" t="s">
+      <c r="D52" s="158" t="s">
         <v>154</v>
-      </c>
-      <c r="D52" s="158" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="53">
@@ -2078,206 +2073,206 @@
         <v>168</v>
       </c>
       <c r="C56" s="173" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D56" s="174" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="175" t="s">
+        <v>169</v>
+      </c>
+      <c r="B57" s="176" t="s">
         <v>170</v>
       </c>
-      <c r="B57" s="176" t="s">
+      <c r="C57" s="177" t="s">
         <v>171</v>
       </c>
-      <c r="C57" s="177" t="s">
+      <c r="D57" s="178" t="s">
         <v>172</v>
-      </c>
-      <c r="D57" s="178" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="179" t="s">
+        <v>173</v>
+      </c>
+      <c r="B58" s="180" t="s">
         <v>174</v>
       </c>
-      <c r="B58" s="180" t="s">
-        <v>175</v>
-      </c>
       <c r="C58" s="181" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D58" s="182" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="183" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="184" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" s="185" t="s">
         <v>177</v>
       </c>
-      <c r="B59" s="184" t="s">
+      <c r="D59" s="186" t="s">
         <v>178</v>
-      </c>
-      <c r="C59" s="185" t="s">
-        <v>179</v>
-      </c>
-      <c r="D59" s="186" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="187" t="s">
+        <v>179</v>
+      </c>
+      <c r="B60" s="188" t="s">
+        <v>180</v>
+      </c>
+      <c r="C60" s="189" t="s">
         <v>181</v>
       </c>
-      <c r="B60" s="188" t="s">
-        <v>182</v>
-      </c>
-      <c r="C60" s="189" t="s">
-        <v>183</v>
-      </c>
       <c r="D60" s="190" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="191" t="s">
+        <v>182</v>
+      </c>
+      <c r="B61" s="192" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" s="193" t="s">
         <v>184</v>
       </c>
-      <c r="B61" s="192" t="s">
+      <c r="D61" s="194" t="s">
         <v>185</v>
-      </c>
-      <c r="C61" s="193" t="s">
-        <v>186</v>
-      </c>
-      <c r="D61" s="194" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="195" t="s">
+        <v>186</v>
+      </c>
+      <c r="B62" s="196" t="s">
+        <v>187</v>
+      </c>
+      <c r="C62" s="197" t="s">
         <v>188</v>
       </c>
-      <c r="B62" s="196" t="s">
+      <c r="D62" s="198" t="s">
         <v>189</v>
-      </c>
-      <c r="C62" s="197" t="s">
-        <v>190</v>
-      </c>
-      <c r="D62" s="198" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="199" t="s">
+        <v>190</v>
+      </c>
+      <c r="B63" s="200" t="s">
+        <v>191</v>
+      </c>
+      <c r="C63" s="201" t="s">
         <v>192</v>
       </c>
-      <c r="B63" s="200" t="s">
+      <c r="D63" s="202" t="s">
         <v>193</v>
-      </c>
-      <c r="C63" s="201" t="s">
-        <v>194</v>
-      </c>
-      <c r="D63" s="202" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="203" t="s">
+        <v>194</v>
+      </c>
+      <c r="B64" s="204" t="s">
+        <v>195</v>
+      </c>
+      <c r="C64" s="205" t="s">
         <v>196</v>
       </c>
-      <c r="B64" s="204" t="s">
+      <c r="D64" s="206" t="s">
         <v>197</v>
-      </c>
-      <c r="C64" s="205" t="s">
-        <v>198</v>
-      </c>
-      <c r="D64" s="206" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="207" t="s">
+        <v>198</v>
+      </c>
+      <c r="B65" s="208" t="s">
+        <v>199</v>
+      </c>
+      <c r="C65" s="209" t="s">
         <v>200</v>
       </c>
-      <c r="B65" s="208" t="s">
-        <v>201</v>
-      </c>
-      <c r="C65" s="209" t="s">
-        <v>202</v>
-      </c>
       <c r="D65" s="210" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="211" t="s">
+        <v>201</v>
+      </c>
+      <c r="B66" s="212" t="s">
+        <v>202</v>
+      </c>
+      <c r="C66" s="213" t="s">
         <v>203</v>
       </c>
-      <c r="B66" s="212" t="s">
+      <c r="D66" s="214" t="s">
         <v>204</v>
-      </c>
-      <c r="C66" s="213" t="s">
-        <v>205</v>
-      </c>
-      <c r="D66" s="214" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="215" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B67" s="216" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C67" s="217" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D67" s="218" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="219" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B68" s="220" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C68" s="221" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D68" s="222" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="223" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B69" s="224" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C69" s="225" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D69" s="226" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="227" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B70" s="228" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C70" s="229" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D70" s="230" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
